--- a/resources/templates/standard/L2100-11.xlsx
+++ b/resources/templates/standard/L2100-11.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>조도 측정 기록일지</t>
   </si>
@@ -580,25 +583,29 @@
     <col min="9" max="11" width="40.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="2" ht="30" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="25.05" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -627,23 +634,23 @@
     </row>
     <row r="5" ht="25.05" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -651,34 +658,34 @@
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="79.95" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
